--- a/Requisitos_PI_Streaming_B2B.xlsx
+++ b/Requisitos_PI_Streaming_B2B.xlsx
@@ -5,34 +5,68 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xanda\OneDrive\Área de Trabalho\SPTECH\2 SEMESTRE\Projeto\documentary-repository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Giovanni\Desktop\documentary-repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{105D7605-CC0E-4EF5-965A-A2D686180E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3B5F866-D782-4DCA-8CE0-99E0554ABACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requisitos FUN PI - Streaming" sheetId="1" r:id="rId1"/>
     <sheet name="Requisitos NF PI - Streaming " sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requisitos FUN PI - Streaming'!$A$7:$M$7</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+  <si>
+    <t>REQUISITOS FUNCIONAIS</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Descrição do Requisito</t>
-  </si>
-  <si>
-    <t>Pontuação (Fibonacci)</t>
+    <t>Requisito</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Classificação</t>
+  </si>
+  <si>
+    <t>Pontos</t>
+  </si>
+  <si>
+    <t>Tam(#)</t>
+  </si>
+  <si>
+    <t>Prioridade</t>
+  </si>
+  <si>
+    <t>Semana</t>
   </si>
   <si>
     <t>RF01</t>
@@ -71,6 +105,9 @@
     <t>RF06</t>
   </si>
   <si>
+    <t xml:space="preserve">O sistema deve criar relatórios executivos </t>
+  </si>
+  <si>
     <t>RF07</t>
   </si>
   <si>
@@ -83,53 +120,92 @@
     <t>O sistema deve permitir filtragem de artistas por métricas específicas.</t>
   </si>
   <si>
+    <t>RF09</t>
+  </si>
+  <si>
+    <t>RF10</t>
+  </si>
+  <si>
+    <t>RF11</t>
+  </si>
+  <si>
+    <t>RF12</t>
+  </si>
+  <si>
+    <t>RF13</t>
+  </si>
+  <si>
+    <t>RF14</t>
+  </si>
+  <si>
+    <t>RF15</t>
+  </si>
+  <si>
+    <t>RF16</t>
+  </si>
+  <si>
+    <t>RF17</t>
+  </si>
+  <si>
+    <t>RF18</t>
+  </si>
+  <si>
+    <t>RF19</t>
+  </si>
+  <si>
+    <t>RF20</t>
+  </si>
+  <si>
+    <t>RF21</t>
+  </si>
+  <si>
+    <t>RF22</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Descrição do Requisito Não Funcional</t>
+  </si>
+  <si>
     <t>RNF01</t>
   </si>
   <si>
+    <t>Desempenho</t>
+  </si>
+  <si>
+    <t>O sistema deve processar a base completa de dados sem travamentos.</t>
+  </si>
+  <si>
     <t>RNF02</t>
   </si>
   <si>
+    <t>Integrabilidade</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir importação de arquivos CSV das bases de dados utilizadas.</t>
+  </si>
+  <si>
     <t>RNF03</t>
   </si>
   <si>
+    <t>Segurança</t>
+  </si>
+  <si>
+    <t>Os dados importados devem ser armazenados de forma segura, evitando alterações indevidas.</t>
+  </si>
+  <si>
     <t>RNF04</t>
   </si>
   <si>
-    <t xml:space="preserve">O sistema deve criar relatórios executivos </t>
-  </si>
-  <si>
-    <t>Desempenho</t>
-  </si>
-  <si>
-    <t>O sistema deve processar a base completa de dados sem travamentos.</t>
-  </si>
-  <si>
-    <t>Integrabilidade</t>
-  </si>
-  <si>
-    <t>O sistema deve permitir importação de arquivos CSV das bases de dados utilizadas.</t>
-  </si>
-  <si>
-    <t>Segurança</t>
-  </si>
-  <si>
-    <t>Os dados importados devem ser armazenados de forma segura, evitando alterações indevidas.</t>
-  </si>
-  <si>
     <t>O sistema deve permitir acesso apenas a usuários autenticados.</t>
-  </si>
-  <si>
-    <t>Categoria</t>
-  </si>
-  <si>
-    <t>Descrição do Requisito Não Funcional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,23 +220,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Montserrat"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA939CF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -183,23 +284,98 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFA939CF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -209,6 +385,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>75534</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>912752</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>64427</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6226551-252C-8086-90E6-EEC45BA0DC34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="75534"/>
+          <a:ext cx="1600771" cy="913650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,222 +727,1002 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="87.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="91" customWidth="1"/>
+    <col min="4" max="5" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+    </row>
+    <row r="7" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G7" s="9"/>
+      <c r="H7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1">
+      <c r="I7" s="9"/>
+      <c r="J7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10">
+        <v>21</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10">
+        <v>13</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+    </row>
+    <row r="11" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10">
+        <v>13</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+    </row>
+    <row r="12" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10">
+        <v>8</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10">
+        <v>21</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+    </row>
+    <row r="14" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10">
+        <v>8</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+    </row>
+    <row r="15" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="3"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+    </row>
+    <row r="16" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+    </row>
+    <row r="18" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+    </row>
+    <row r="19" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+    </row>
+    <row r="21" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+    </row>
+    <row r="26" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+    </row>
+    <row r="27" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+    </row>
+    <row r="29" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
     </row>
   </sheetData>
+  <autoFilter ref="A7:M7" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3" showButton="0"/>
+    <filterColumn colId="5" showButton="0"/>
+    <filterColumn colId="7" showButton="0"/>
+    <filterColumn colId="9" showButton="0"/>
+    <filterColumn colId="11" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="117">
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="A1:B6"/>
+    <mergeCell ref="C1:M6"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F15:G15"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4698B26-FA9F-4412-8EA3-3997D4FD1A93}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="90.42578125" customWidth="1"/>
-    <col min="4" max="4" width="45.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="90.44140625" customWidth="1"/>
+    <col min="4" max="4" width="45.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A729CFA7192B0F4AA60BE2DF65F4BC74" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7679e9f1a86762f1044b3dbc4bf64f1c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90c901f349532e4d4ac0d21813751a98" ns3:_="">
+    <xsd:import namespace="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887A3EAE-BBEF-4C58-A035-C46B9F6446FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F40F310-7C69-40B9-8659-12C58DCC6598}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2114E23-3E7F-480B-8E2B-AF214FAECA54}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Requisitos_PI_Streaming_B2B.xlsx
+++ b/Requisitos_PI_Streaming_B2B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Giovanni\Desktop\documentary-repository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xanda\OneDrive\Área de Trabalho\SPTECH\2 SEMESTRE\Projeto\documentary-repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3B5F866-D782-4DCA-8CE0-99E0554ABACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850F2B89-6530-4AEC-9E11-7A4F344127B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requisitos FUN PI - Streaming" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
   <si>
     <t>REQUISITOS FUNCIONAIS</t>
   </si>
@@ -75,51 +75,27 @@
     <t>Funcional</t>
   </si>
   <si>
-    <t>O sistema deve consolidar métricas de Spotify e YouTube em um painel único.</t>
-  </si>
-  <si>
     <t>RF02</t>
   </si>
   <si>
-    <t>O sistema deve permitir comparação lado a lado entre artistas com indicadores padronizados.</t>
-  </si>
-  <si>
     <t>RF03</t>
   </si>
   <si>
-    <t>O sistema deve calcular um Score de Potencial Estrutural baseado em métricas derivadas.</t>
-  </si>
-  <si>
     <t>RF04</t>
   </si>
   <si>
-    <t>O sistema deve calcular métricas proporcionais como Streams/Followers e Likes/Views.</t>
-  </si>
-  <si>
     <t>RF05</t>
   </si>
   <si>
-    <t>O sistema deve gerar ranking de artistas com base nos indicadores estruturais.</t>
-  </si>
-  <si>
     <t>RF06</t>
   </si>
   <si>
-    <t xml:space="preserve">O sistema deve criar relatórios executivos </t>
-  </si>
-  <si>
     <t>RF07</t>
   </si>
   <si>
-    <t>O sistema deve identificar discrepâncias entre volume e engajamento.</t>
-  </si>
-  <si>
     <t>RF08</t>
   </si>
   <si>
-    <t>O sistema deve permitir filtragem de artistas por métricas específicas.</t>
-  </si>
-  <si>
     <t>RF09</t>
   </si>
   <si>
@@ -199,13 +175,52 @@
   </si>
   <si>
     <t>O sistema deve permitir acesso apenas a usuários autenticados.</t>
+  </si>
+  <si>
+    <t>O sistema deve exibir um dashboard geral de artistas contendo barra de busca, filtros por gênero e categoria (Famoso, Emergente, Underground), KPIs de média de popularidade, total de streams e média de engajamento, além de uma tabela com nome do artista, popularidade, seguidores, streams, visualizações, engajamento e botão para visualizar detalhes.</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir selecionar dois ou mais artistas para comparação, exibindo gráfico comparativo e tabela com métricas de popularidade, número de seguidores, total de streams, visualizações, likes e taxa de engajamento de cada artista.</t>
+  </si>
+  <si>
+    <t>O sistema deve apresentar uma tela de análise detalhada da música contendo nome da música, artista, gênero, popularidade, KPIs de streams, visualizações, likes e engajamento, além de gráfico radar com atributos musicais (danceability, energy, valence, acousticness, instrumentalness) e informações técnicas como BPM.</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir criar set-lists selecionando músicas da base, registrando nome da lista, data de criação e músicas selecionadas com seus respectivos artistas, popularidade e streams.</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>O sistema deve gerar um dashboard analítico para cada set-list criada, exibindo KPIs como média de energy, média de danceability e distribuição de gêneros musicais em gráficos.</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>O sistema deve classificar automaticamente os artistas nas categorias Famoso, Emergente ou Underground, exibindo essa classificação na tabela e na página de detalhes do artista.</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>O sistema deve exibir um gráfico radar com os atributos musicais de uma música selecionada, apresentando os valores de energy, danceability, valence, loudness, speechiness e instrumentalness, além de informações complementares como nome da música, artista, popularidade, streams, views e likes para análise</t>
+  </si>
+  <si>
+    <t>O sistema deve apresentar uma tela de diagnóstico detalhado de uma música contendo nome da música, artista e álbum, KPIs de streams, views, likes e comentários, cálculo de taxa de engajamento (likes/views e comments/views) e visualizações gráficas dos atributos musicais energy, danceability, valence, loudness, speechiness e instrumentalness para análise completa de desempenho e perfil sonoro.</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir selecionar duas ou mais músicas para comparação, exibindo gráficos e tabela comparativa contendo nome da música, artista, streams, views, likes, comentários, taxa de engajamento e atributos musicais (energy, danceability, valence, loudness, speechiness e instrumentalness) para avaliar diferenças de performance e características sonoras entre as faixas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +254,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Montserrat"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -323,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -338,21 +361,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -365,6 +373,26 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,108 +755,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="91" customWidth="1"/>
-    <col min="4" max="5" width="8.44140625" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" customWidth="1"/>
+    <col min="4" max="5" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="13" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-    </row>
-    <row r="7" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+    </row>
+    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
@@ -838,476 +866,500 @@
       <c r="C7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="8" t="s">
+      <c r="G7" s="11"/>
+      <c r="H7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="11"/>
+      <c r="J7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="8" t="s">
+      <c r="K7" s="11"/>
+      <c r="L7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="9"/>
-    </row>
-    <row r="8" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6" t="s">
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" spans="1:16" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14">
+        <v>21</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+    </row>
+    <row r="9" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10">
+      <c r="B9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14">
+        <v>21</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14">
+        <v>21</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+    </row>
+    <row r="11" spans="1:16" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-    </row>
-    <row r="9" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14">
         <v>13</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10">
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="P11" s="17"/>
+    </row>
+    <row r="12" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14">
+        <v>13</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+    </row>
+    <row r="13" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14">
+        <v>13</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="P13" s="16"/>
+    </row>
+    <row r="14" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14">
+        <v>13</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+    </row>
+    <row r="15" spans="1:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14">
+        <v>13</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+    </row>
+    <row r="16" spans="1:16" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14">
+        <v>8</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+    </row>
+    <row r="17" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+    </row>
+    <row r="18" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+    </row>
+    <row r="19" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-    </row>
-    <row r="10" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10">
-        <v>13</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-    </row>
-    <row r="11" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10">
-        <v>13</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10">
-        <v>8</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10">
-        <v>21</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6" t="s">
+      <c r="B19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+    </row>
+    <row r="20" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B20" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+    </row>
+    <row r="21" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10">
-        <v>8</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6" t="s">
+      <c r="B21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+    </row>
+    <row r="22" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+    </row>
+    <row r="23" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10">
-        <v>5</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="6" t="s">
+      <c r="B23" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+    </row>
+    <row r="24" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-    </row>
-    <row r="17" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="6" t="s">
+      <c r="B24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+    </row>
+    <row r="25" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="6" t="s">
+      <c r="B25" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+    </row>
+    <row r="26" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6" t="s">
+      <c r="B26" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+    </row>
+    <row r="27" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="6" t="s">
+      <c r="B27" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+    </row>
+    <row r="28" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-    </row>
-    <row r="21" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="6" t="s">
+      <c r="B28" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+    </row>
+    <row r="29" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-    </row>
-    <row r="22" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-    </row>
-    <row r="23" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-    </row>
-    <row r="24" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-    </row>
-    <row r="25" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-    </row>
-    <row r="26" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-    </row>
-    <row r="27" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-    </row>
-    <row r="28" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-    </row>
-    <row r="29" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
+      <c r="B29" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:M7" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -1318,69 +1370,36 @@
     <filterColumn colId="11" showButton="0"/>
   </autoFilter>
   <mergeCells count="117">
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="A1:B6"/>
+    <mergeCell ref="C1:M6"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H11:I11"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="L15:M15"/>
     <mergeCell ref="L14:M14"/>
@@ -1405,36 +1424,69 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="A1:B6"/>
-    <mergeCell ref="C1:M6"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1446,70 +1498,70 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4698B26-FA9F-4412-8EA3-3997D4FD1A93}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="90.44140625" customWidth="1"/>
-    <col min="4" max="4" width="45.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="90.42578125" customWidth="1"/>
+    <col min="4" max="4" width="45.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -1669,20 +1721,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1704,14 +1756,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F40F310-7C69-40B9-8659-12C58DCC6598}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2114E23-3E7F-480B-8E2B-AF214FAECA54}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -1725,4 +1769,12 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F40F310-7C69-40B9-8659-12C58DCC6598}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>